--- a/Models/Свиньи/Датасет по свиньям wide.xlsx
+++ b/Models/Свиньи/Датасет по свиньям wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7877,6 +7877,475 @@
         <v>5.7</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>263.72</v>
+      </c>
+      <c r="C122" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="D122" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>347.69</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J122" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="K122" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="L122" t="n">
+        <v>614.67</v>
+      </c>
+      <c r="M122" t="n">
+        <v>829.5600000000001</v>
+      </c>
+      <c r="N122" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>130.43</v>
+      </c>
+      <c r="R122" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1227.05</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1689.17</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>340.79</v>
+      </c>
+      <c r="C123" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D123" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>288.64</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K123" t="n">
+        <v>168.6</v>
+      </c>
+      <c r="L123" t="n">
+        <v>650.0400000000001</v>
+      </c>
+      <c r="M123" t="n">
+        <v>555.74</v>
+      </c>
+      <c r="N123" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="R123" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1408.94</v>
+      </c>
+      <c r="T123" t="n">
+        <v>1721.94</v>
+      </c>
+      <c r="U123" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>447.27</v>
+      </c>
+      <c r="C124" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="D124" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>272.95</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J124" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="K124" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="L124" t="n">
+        <v>879.3000000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>195.42</v>
+      </c>
+      <c r="N124" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>208.34</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1867.97</v>
+      </c>
+      <c r="T124" t="n">
+        <v>1684</v>
+      </c>
+      <c r="U124" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>467.44</v>
+      </c>
+      <c r="C125" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>274.8100000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="K125" t="n">
+        <v>213.8</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1052.23</v>
+      </c>
+      <c r="M125" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="N125" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>165.61</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1494.22</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1852.75</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>306.14</v>
+      </c>
+      <c r="C126" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>287.1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K126" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1181.78</v>
+      </c>
+      <c r="M126" t="n">
+        <v>116.23</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>174.63</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1512.88</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1591.07</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>694.22</v>
+      </c>
+      <c r="C127" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="D127" t="n">
+        <v>38</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J127" t="n">
+        <v>83.19999999999999</v>
+      </c>
+      <c r="K127" t="n">
+        <v>180.1</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1087.37</v>
+      </c>
+      <c r="M127" t="n">
+        <v>195.09</v>
+      </c>
+      <c r="N127" t="n">
+        <v>3</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>590.36</v>
+      </c>
+      <c r="R127" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1586.88</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1441.53</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>803.75</v>
+      </c>
+      <c r="C128" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>268.94</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J128" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="L128" t="n">
+        <v>842.5799999999999</v>
+      </c>
+      <c r="M128" t="n">
+        <v>183.42</v>
+      </c>
+      <c r="N128" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>195.49</v>
+      </c>
+      <c r="R128" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1529.18</v>
+      </c>
+      <c r="T128" t="n">
+        <v>2780.05</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
